--- a/duoki_editor/resources/data/blank/服装店-变颜色-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/服装店-变颜色-1-blank.xlsx
@@ -139,7 +139,7 @@
     <t>接下来请找到`{word_cn}！{word_en}`</t>
   </si>
   <si>
-    <t>现在请找出来{word_cn}的位置！"{word_en}"</t>
+    <t>现在请找出{word_cn}的位置！"{word_en}"</t>
   </si>
   <si>
     <t>这是最后一个衣服了，快找到{word_cn}吧！"{word_en}"</t>
@@ -148,7 +148,7 @@
     <t>找不到的话，要不要打开魔镜试试？快告诉我吧</t>
   </si>
   <si>
-    <t>{user_name}快看这里！我们用魔镜找到他吧。</t>
+    <t>{user_name}快看这里！我们用魔镜找到它吧。</t>
   </si>
   <si>
     <t>为了找到{word_cn}，需要大声念出咒语，"{word_en}"！</t>
@@ -157,7 +157,7 @@
     <t>我来帮你！"{word_en}"</t>
   </si>
   <si>
-    <t>为了把他们装在好看的包装袋里！大声说出{word_cn}的英文名字吧！</t>
+    <t>为了把衣物装在好看的包装袋里！大声说出{word_cn}的英文名字吧！</t>
   </si>
   <si>
     <t>跟我一起读吧！"{word_en}"</t>
